--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/MONTANA_2023.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/MONTANA_2023.xlsx
@@ -351,40 +351,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D171"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="C2">
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CALVILLO</t>
+          <t>Calvillo</t>
         </is>
       </c>
       <c r="C3">
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C4">
@@ -423,12 +433,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAMPECHE</t>
+          <t>Campeche</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ESCÁRCEGA</t>
+          <t>Escárcega</t>
         </is>
       </c>
       <c r="C5">
@@ -439,9 +449,14 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C6">
@@ -454,12 +469,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHIAPAS</t>
+          <t>Chiapas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ACACOYAGUA</t>
+          <t>Acacoyagua</t>
         </is>
       </c>
       <c r="C7">
@@ -470,9 +485,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ANGEL ALBINO CORZO</t>
+          <t>Angel Albino Corzo</t>
         </is>
       </c>
       <c r="C8">
@@ -483,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EL BOSQUE</t>
+          <t>El Bosque</t>
         </is>
       </c>
       <c r="C9">
@@ -496,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FRONTERA COMALAPA</t>
+          <t>Frontera Comalapa</t>
         </is>
       </c>
       <c r="C10">
@@ -509,9 +539,14 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IXTAPA</t>
+          <t>Ixtapa</t>
         </is>
       </c>
       <c r="C11">
@@ -522,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MAPASTEPEC</t>
+          <t>Mapastepec</t>
         </is>
       </c>
       <c r="C12">
@@ -535,9 +575,14 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MITONTIC</t>
+          <t>Mitontic</t>
         </is>
       </c>
       <c r="C13">
@@ -548,9 +593,14 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OCOSINGO</t>
+          <t>Ocosingo</t>
         </is>
       </c>
       <c r="C14">
@@ -561,9 +611,14 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OCOTEPEC</t>
+          <t>Ocotepec</t>
         </is>
       </c>
       <c r="C15">
@@ -574,9 +629,14 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PALENQUE</t>
+          <t>Palenque</t>
         </is>
       </c>
       <c r="C16">
@@ -587,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SAN CRISTÓBAL DE LAS CASAS</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C17">
@@ -600,9 +665,14 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SILTEPEC</t>
+          <t>Siltepec</t>
         </is>
       </c>
       <c r="C18">
@@ -613,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SIMOJOVEL</t>
+          <t>Simojovel</t>
         </is>
       </c>
       <c r="C19">
@@ -626,9 +701,14 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TAPACHULA</t>
+          <t>Tapachula</t>
         </is>
       </c>
       <c r="C20">
@@ -639,9 +719,14 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TECPATÁN</t>
+          <t>Tecpatán</t>
         </is>
       </c>
       <c r="C21">
@@ -652,9 +737,14 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TUXTLA GUTIÉRREZ</t>
+          <t>Tuxtla Gutiérrez</t>
         </is>
       </c>
       <c r="C22">
@@ -665,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VILLAFLORES</t>
+          <t>Villaflores</t>
         </is>
       </c>
       <c r="C23">
@@ -678,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C24">
@@ -693,12 +793,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BUENAVENTURA</t>
+          <t>Buenaventura</t>
         </is>
       </c>
       <c r="C25">
@@ -709,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="C26">
@@ -722,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CUAUHTÉMOC</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="C27">
@@ -735,9 +845,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IGNACIO ZARAGOZA</t>
+          <t>Ignacio Zaragoza</t>
         </is>
       </c>
       <c r="C28">
@@ -748,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JUÁREZ</t>
+          <t>Juárez</t>
         </is>
       </c>
       <c r="C29">
@@ -761,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NUEVO CASAS GRANDES</t>
+          <t>Nuevo Casas Grandes</t>
         </is>
       </c>
       <c r="C30">
@@ -774,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SAUCILLO</t>
+          <t>Saucillo</t>
         </is>
       </c>
       <c r="C31">
@@ -787,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C32">
@@ -802,12 +937,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CIUDAD DE MÉXICO</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BENITO JUÁREZ</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="C33">
@@ -818,9 +953,14 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CUAUHTÉMOC</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="C34">
@@ -831,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GUSTAVO A. MADERO</t>
+          <t>Gustavo A. Madero</t>
         </is>
       </c>
       <c r="C35">
@@ -844,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IZTAPALAPA</t>
+          <t>Iztapalapa</t>
         </is>
       </c>
       <c r="C36">
@@ -857,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MIGUEL HIDALGO</t>
+          <t>Miguel Hidalgo</t>
         </is>
       </c>
       <c r="C37">
@@ -870,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C38">
@@ -885,12 +1045,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>COAHUILA DE ZARAGOZA</t>
+          <t>Coahuila De Zaragoza</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MÚZQUIZ</t>
+          <t>Múzquiz</t>
         </is>
       </c>
       <c r="C39">
@@ -901,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PIEDRAS NEGRAS</t>
+          <t>Piedras Negras</t>
         </is>
       </c>
       <c r="C40">
@@ -914,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TORREÓN</t>
+          <t>Torreón</t>
         </is>
       </c>
       <c r="C41">
@@ -927,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C42">
@@ -942,12 +1117,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DURANGO</t>
+          <t>Durango</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CANATLÁN</t>
+          <t>Canatlán</t>
         </is>
       </c>
       <c r="C43">
@@ -958,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DURANGO</t>
+          <t>Durango</t>
         </is>
       </c>
       <c r="C44">
@@ -971,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GUADALUPE VICTORIA</t>
+          <t>Guadalupe Victoria</t>
         </is>
       </c>
       <c r="C45">
@@ -984,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MAPIMÍ</t>
+          <t>Mapimí</t>
         </is>
       </c>
       <c r="C46">
@@ -997,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VICENTE GUERRERO</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C47">
@@ -1010,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C48">
@@ -1025,12 +1225,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ESTADO DE MÉXICO</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ACAMBAY DE RUÍZ CASTAÑEDA</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C49">
@@ -1041,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ATLACOMULCO</t>
+          <t>Atlacomulco</t>
         </is>
       </c>
       <c r="C50">
@@ -1054,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ECATEPEC DE MORELOS</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C51">
@@ -1067,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JOCOTITLÁN</t>
+          <t>Jocotitlán</t>
         </is>
       </c>
       <c r="C52">
@@ -1080,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NEZAHUALCÓYOTL</t>
+          <t>Nezahualcóyotl</t>
         </is>
       </c>
       <c r="C53">
@@ -1093,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SAN FELIPE DEL PROGRESO</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C54">
@@ -1106,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TENANCINGO</t>
+          <t>Tenancingo</t>
         </is>
       </c>
       <c r="C55">
@@ -1119,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TOLUCA</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="C56">
@@ -1132,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VILLA GUERRERO</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C57">
@@ -1145,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VILLA VICTORIA</t>
+          <t>Villa Victoria</t>
         </is>
       </c>
       <c r="C58">
@@ -1158,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C59">
@@ -1173,12 +1423,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ACÁMBARO</t>
+          <t>Acámbaro</t>
         </is>
       </c>
       <c r="C60">
@@ -1189,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>APASEO EL ALTO</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C61">
@@ -1202,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CELAYA</t>
+          <t>Celaya</t>
         </is>
       </c>
       <c r="C62">
@@ -1215,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DOCTOR MORA</t>
+          <t>Doctor Mora</t>
         </is>
       </c>
       <c r="C63">
@@ -1228,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="C64">
@@ -1241,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LEÓN</t>
+          <t>León</t>
         </is>
       </c>
       <c r="C65">
@@ -1254,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ROMITA</t>
+          <t>Romita</t>
         </is>
       </c>
       <c r="C66">
@@ -1267,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SAN LUIS DE LA PAZ</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C67">
@@ -1280,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SAN MIGUEL DE ALLENDE</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C68">
@@ -1293,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SANTA CRUZ DE JUVENTINO ROSAS</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C69">
@@ -1306,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SILAO DE LA VICTORIA</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C70">
@@ -1319,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VILLAGRÁN</t>
+          <t>Villagrán</t>
         </is>
       </c>
       <c r="C71">
@@ -1332,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C72">
@@ -1347,12 +1657,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ATOYAC DE ÁLVAREZ</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C73">
@@ -1363,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CHILPANCINGO DE LOS BRAVO</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C74">
@@ -1376,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>COYUCA DE BENÍTEZ</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C75">
@@ -1389,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TECOANAPA</t>
+          <t>Tecoanapa</t>
         </is>
       </c>
       <c r="C76">
@@ -1402,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TÉCPAN DE GALEANA</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C77">
@@ -1415,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ZIRÁNDARO</t>
+          <t>Zirándaro</t>
         </is>
       </c>
       <c r="C78">
@@ -1428,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C79">
@@ -1443,12 +1783,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>Hidalgo</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>IXMIQUILPAN</t>
+          <t>Ixmiquilpan</t>
         </is>
       </c>
       <c r="C80">
@@ -1459,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PACHUCA DE SOTO</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C81">
@@ -1472,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TEZONTEPEC DE ALDAMA</t>
+          <t>Tezontepec De Aldama</t>
         </is>
       </c>
       <c r="C82">
@@ -1485,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TULANCINGO DE BRAVO</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C83">
@@ -1498,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C84">
@@ -1513,12 +1873,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>JALISCO</t>
+          <t>Jalisco</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AUTLÁN DE NAVARRO</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C85">
@@ -1529,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>AYUTLA</t>
+          <t>Ayutla</t>
         </is>
       </c>
       <c r="C86">
@@ -1542,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CABO CORRIENTES</t>
+          <t>Cabo Corrientes</t>
         </is>
       </c>
       <c r="C87">
@@ -1555,9 +1925,14 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CASIMIRO CASTILLO</t>
+          <t>Casimiro Castillo</t>
         </is>
       </c>
       <c r="C88">
@@ -1568,9 +1943,14 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>COLOTLÁN</t>
+          <t>Colotlán</t>
         </is>
       </c>
       <c r="C89">
@@ -1581,9 +1961,14 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GUADALAJARA</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="C90">
@@ -1594,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JESÚS MARÍA</t>
+          <t>Jesús María</t>
         </is>
       </c>
       <c r="C91">
@@ -1607,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LAGOS DE MORENO</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C92">
@@ -1620,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>OJUELOS DE JALISCO</t>
+          <t>Ojuelos De Jalisco</t>
         </is>
       </c>
       <c r="C93">
@@ -1633,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SAN GABRIEL</t>
+          <t>San Gabriel</t>
         </is>
       </c>
       <c r="C94">
@@ -1646,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SAN JUAN DE LOS LAGOS</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C95">
@@ -1659,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TEQUILA</t>
+          <t>Tequila</t>
         </is>
       </c>
       <c r="C96">
@@ -1672,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TIZAPÁN EL ALTO</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C97">
@@ -1685,9 +2105,14 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TOLIMÁN</t>
+          <t>Tolimán</t>
         </is>
       </c>
       <c r="C98">
@@ -1698,9 +2123,14 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TOMATLÁN</t>
+          <t>Tomatlán</t>
         </is>
       </c>
       <c r="C99">
@@ -1711,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ZAPOPAN</t>
+          <t>Zapopan</t>
         </is>
       </c>
       <c r="C100">
@@ -1724,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C101">
@@ -1739,12 +2179,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MICHOACÁN DE OCAMPO</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>Hidalgo</t>
         </is>
       </c>
       <c r="C102">
@@ -1755,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PARACHO</t>
+          <t>Paracho</t>
         </is>
       </c>
       <c r="C103">
@@ -1768,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PÁTZCUARO</t>
+          <t>Pátzcuaro</t>
         </is>
       </c>
       <c r="C104">
@@ -1781,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TLALPUJAHUA</t>
+          <t>Tlalpujahua</t>
         </is>
       </c>
       <c r="C105">
@@ -1794,9 +2249,14 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>URUAPAN</t>
+          <t>Uruapan</t>
         </is>
       </c>
       <c r="C106">
@@ -1807,9 +2267,14 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C107">
@@ -1822,12 +2287,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NAYARIT</t>
+          <t>Nayarit</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DEL NAYAR</t>
+          <t>Del Nayar</t>
         </is>
       </c>
       <c r="C108">
@@ -1838,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SAN BLAS</t>
+          <t>San Blas</t>
         </is>
       </c>
       <c r="C109">
@@ -1851,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SANTIAGO IXCUINTLA</t>
+          <t>Santiago Ixcuintla</t>
         </is>
       </c>
       <c r="C110">
@@ -1864,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TUXPAN</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C111">
@@ -1877,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C112">
@@ -1892,12 +2377,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NUEVO LEÓN</t>
+          <t>Nuevo León</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SABINAS HIDALGO</t>
+          <t>Sabinas Hidalgo</t>
         </is>
       </c>
       <c r="C113">
@@ -1908,9 +2393,14 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C114">
@@ -1923,12 +2413,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>OAXACA</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SAN JUAN LACHAO</t>
+          <t>San Juan Lachao</t>
         </is>
       </c>
       <c r="C115">
@@ -1939,9 +2429,14 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SAN LUCAS ZOQUIÁPAM</t>
+          <t>San Lucas Zoquiápam</t>
         </is>
       </c>
       <c r="C116">
@@ -1952,9 +2447,14 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SANTA MARÍA CHIMALAPA</t>
+          <t>Santa María Chimalapa</t>
         </is>
       </c>
       <c r="C117">
@@ -1965,9 +2465,14 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SANTA MARÍA TONAMECA</t>
+          <t>Santa María Tonameca</t>
         </is>
       </c>
       <c r="C118">
@@ -1978,9 +2483,14 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TLACOLULA DE MATAMOROS</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C119">
@@ -1991,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C120">
@@ -2006,12 +2521,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>AJALPAN</t>
+          <t>Ajalpan</t>
         </is>
       </c>
       <c r="C121">
@@ -2022,9 +2537,14 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CHIGNAHUAPAN</t>
+          <t>Chignahuapan</t>
         </is>
       </c>
       <c r="C122">
@@ -2035,9 +2555,14 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CUYOACO</t>
+          <t>Cuyoaco</t>
         </is>
       </c>
       <c r="C123">
@@ -2048,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>JALPAN</t>
+          <t>Jalpan</t>
         </is>
       </c>
       <c r="C124">
@@ -2061,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="C125">
@@ -2074,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SAN MARTÍN TOTOLTEPEC</t>
+          <t>San Martín Totoltepec</t>
         </is>
       </c>
       <c r="C126">
@@ -2087,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>VICENTE GUERRERO</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C127">
@@ -2100,9 +2645,14 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ZACATLÁN</t>
+          <t>Zacatlán</t>
         </is>
       </c>
       <c r="C128">
@@ -2113,9 +2663,14 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C129">
@@ -2128,12 +2683,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>JALPAN DE SERRA</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C130">
@@ -2144,9 +2699,14 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="C131">
@@ -2157,9 +2717,14 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TEQUISQUIAPAN</t>
+          <t>Tequisquiapan</t>
         </is>
       </c>
       <c r="C132">
@@ -2170,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C133">
@@ -2185,12 +2755,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CIUDAD VALLES</t>
+          <t>Ciudad Valles</t>
         </is>
       </c>
       <c r="C134">
@@ -2201,9 +2771,14 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EBANO</t>
+          <t>Ebano</t>
         </is>
       </c>
       <c r="C135">
@@ -2214,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MEXQUITIC DE CARMONA</t>
+          <t>Mexquitic De Carmona</t>
         </is>
       </c>
       <c r="C136">
@@ -2227,9 +2807,14 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SALINAS</t>
+          <t>Salinas</t>
         </is>
       </c>
       <c r="C137">
@@ -2240,9 +2825,14 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="C138">
@@ -2253,9 +2843,14 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>VILLA DE RAMOS</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C139">
@@ -2266,9 +2861,14 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>XILITLA</t>
+          <t>Xilitla</t>
         </is>
       </c>
       <c r="C140">
@@ -2279,9 +2879,14 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C141">
@@ -2294,12 +2899,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SINALOA</t>
+          <t>Sinaloa</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>AHOME</t>
+          <t>Ahome</t>
         </is>
       </c>
       <c r="C142">
@@ -2310,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C143">
@@ -2325,12 +2935,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SONORA</t>
+          <t>Sonora</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CAJEME</t>
+          <t>Cajeme</t>
         </is>
       </c>
       <c r="C144">
@@ -2341,9 +2951,14 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C145">
@@ -2356,12 +2971,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TAMAULIPAS</t>
+          <t>Tamaulipas</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>VICTORIA</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C146">
@@ -2372,9 +2987,14 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C147">
@@ -2387,12 +3007,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ALPATLÁHUAC</t>
+          <t>Alpatláhuac</t>
         </is>
       </c>
       <c r="C148">
@@ -2403,9 +3023,14 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ATLAHUILCO</t>
+          <t>Atlahuilco</t>
         </is>
       </c>
       <c r="C149">
@@ -2416,9 +3041,14 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CALCAHUALCO</t>
+          <t>Calcahualco</t>
         </is>
       </c>
       <c r="C150">
@@ -2429,9 +3059,14 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>COSCOMATEPEC</t>
+          <t>Coscomatepec</t>
         </is>
       </c>
       <c r="C151">
@@ -2442,9 +3077,14 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ESPINAL</t>
+          <t>Espinal</t>
         </is>
       </c>
       <c r="C152">
@@ -2455,9 +3095,14 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>HUAYACOCOTLA</t>
+          <t>Huayacocotla</t>
         </is>
       </c>
       <c r="C153">
@@ -2468,9 +3113,14 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>LA ANTIGUA</t>
+          <t>La Antigua</t>
         </is>
       </c>
       <c r="C154">
@@ -2481,9 +3131,14 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MIXTLA DE ALTAMIRANO</t>
+          <t>Mixtla De Altamirano</t>
         </is>
       </c>
       <c r="C155">
@@ -2494,9 +3149,14 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NO SE REGISTRÓ EL MUNICIPIO/CONDADO/ALCALDÍA DE NACIMIENTO</t>
+          <t>No Se Registró El Municipio/Condado/Alcaldía De Nacimiento</t>
         </is>
       </c>
       <c r="C156">
@@ -2507,9 +3167,14 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ORIZABA</t>
+          <t>Orizaba</t>
         </is>
       </c>
       <c r="C157">
@@ -2520,9 +3185,14 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>VERACRUZ</t>
+          <t>Veracruz</t>
         </is>
       </c>
       <c r="C158">
@@ -2533,9 +3203,14 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ZONGOLICA</t>
+          <t>Zongolica</t>
         </is>
       </c>
       <c r="C159">
@@ -2546,9 +3221,14 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C160">
@@ -2561,12 +3241,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ZACATECAS</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>FRESNILLO</t>
+          <t>Fresnillo</t>
         </is>
       </c>
       <c r="C161">
@@ -2577,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>GUADALUPE</t>
+          <t>Guadalupe</t>
         </is>
       </c>
       <c r="C162">
@@ -2590,9 +3275,14 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>OJOCALIENTE</t>
+          <t>Ojocaliente</t>
         </is>
       </c>
       <c r="C163">
@@ -2603,9 +3293,14 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C164">
@@ -2618,7 +3313,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C165">
@@ -2626,41 +3321,6 @@
       </c>
       <c r="D165">
         <v>1</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 789,030</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Noviembre de 2024</t>
-        </is>
       </c>
     </row>
   </sheetData>
